--- a/data/trans_orig/IP19C03-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP19C03-Edad-trans_orig.xlsx
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5645</t>
+          <t>6007</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15263</t>
+          <t>15636</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3779</t>
+          <t>4030</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11984</t>
+          <t>11950</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11421</t>
+          <t>11125</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23824</t>
+          <t>23158</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,06%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>69072</t>
+          <t>68699</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>78690</t>
+          <t>78328</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>81,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>68434</t>
+          <t>68468</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>76639</t>
+          <t>76388</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>85,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>140929</t>
+          <t>141595</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>153332</t>
+          <t>153628</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,25%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13640</t>
+          <t>13945</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26521</t>
+          <t>25992</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12151</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25143</t>
+          <t>24281</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28491</t>
+          <t>28967</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45565</t>
+          <t>46774</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,83%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>72672</t>
+          <t>73201</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>85553</t>
+          <t>85248</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,26%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>80576</t>
+          <t>81438</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>93568</t>
+          <t>93671</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>159347</t>
+          <t>158138</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>176421</t>
+          <t>175945</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>77,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>85,86%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34751</t>
+          <t>35023</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>53266</t>
+          <t>54293</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29990</t>
+          <t>29954</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48414</t>
+          <t>48416</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>68653</t>
+          <t>69361</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>94837</t>
+          <t>95925</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>28,45%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>110231</t>
+          <t>109204</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>128746</t>
+          <t>128474</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,74%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>125287</t>
+          <t>125285</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>143711</t>
+          <t>143747</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>242360</t>
+          <t>241272</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>268544</t>
+          <t>267836</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>79,43%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>61716</t>
+          <t>62455</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>87218</t>
+          <t>85858</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>52195</t>
+          <t>52878</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>76163</t>
+          <t>75264</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>120886</t>
+          <t>119633</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>152067</t>
+          <t>152819</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,44%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>263712</t>
+          <t>265072</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>289214</t>
+          <t>288475</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>285568</t>
+          <t>286467</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>309536</t>
+          <t>308853</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>560594</t>
+          <t>559842</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>591775</t>
+          <t>593028</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>83,21%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3863</t>
+          <t>3660</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12481</t>
+          <t>12155</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7895</t>
+          <t>7865</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19808</t>
+          <t>19519</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13516</t>
+          <t>13317</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27238</t>
+          <t>27304</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,08%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>65207</t>
+          <t>65533</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>73825</t>
+          <t>74028</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>72256</t>
+          <t>72545</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>84169</t>
+          <t>84199</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>142513</t>
+          <t>142447</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>156235</t>
+          <t>156434</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>92,16%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18872</t>
+          <t>18815</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33943</t>
+          <t>34443</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19040</t>
+          <t>19054</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33746</t>
+          <t>33850</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>42190</t>
+          <t>41850</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>63066</t>
+          <t>61895</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,13%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>90505</t>
+          <t>90005</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>105576</t>
+          <t>105633</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>72,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>98340</t>
+          <t>98236</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>113046</t>
+          <t>113032</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>193468</t>
+          <t>194639</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>214344</t>
+          <t>214684</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>75,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,69%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30944</t>
+          <t>31584</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>48574</t>
+          <t>48769</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26135</t>
+          <t>25034</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42084</t>
+          <t>41954</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>61046</t>
+          <t>60858</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>84299</t>
+          <t>84419</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,14%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>99346</t>
+          <t>99151</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>116976</t>
+          <t>116336</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>67,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>78,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>99671</t>
+          <t>99801</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>115620</t>
+          <t>116721</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>70,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>205376</t>
+          <t>205256</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>228629</t>
+          <t>228817</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>78,99%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>61062</t>
+          <t>60546</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>85384</t>
+          <t>84849</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>58221</t>
+          <t>59864</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>83474</t>
+          <t>83812</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>126829</t>
+          <t>125795</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>162877</t>
+          <t>161024</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,37%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>267969</t>
+          <t>268504</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>292291</t>
+          <t>292807</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>283100</t>
+          <t>282762</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>308353</t>
+          <t>306710</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,23%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>557050</t>
+          <t>558903</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>593098</t>
+          <t>594132</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>82,53%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6118</t>
+          <t>6522</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16315</t>
+          <t>16510</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7008</t>
+          <t>6878</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17507</t>
+          <t>17031</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15555</t>
+          <t>15313</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29756</t>
+          <t>29540</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,67%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>51745</t>
+          <t>51550</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>61942</t>
+          <t>61538</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,01%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>64622</t>
+          <t>65098</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>75121</t>
+          <t>75251</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,68%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>120433</t>
+          <t>120649</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>134634</t>
+          <t>134876</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,8%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16068</t>
+          <t>15406</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30690</t>
+          <t>29752</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17502</t>
+          <t>17553</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32467</t>
+          <t>32589</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>38004</t>
+          <t>37158</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>58086</t>
+          <t>59121</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,82%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>118227</t>
+          <t>119165</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>132849</t>
+          <t>133511</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>116874</t>
+          <t>116752</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>131839</t>
+          <t>131788</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,26%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>240172</t>
+          <t>239137</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>260254</t>
+          <t>261100</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,54%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21386</t>
+          <t>21586</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36647</t>
+          <t>36508</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22913</t>
+          <t>23509</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39887</t>
+          <t>40255</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>49190</t>
+          <t>49535</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>71570</t>
+          <t>71716</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,51%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>108458</t>
+          <t>108597</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>123719</t>
+          <t>123519</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>74,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>96118</t>
+          <t>95750</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>113092</t>
+          <t>112496</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,67%</t>
+          <t>70,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>209540</t>
+          <t>209394</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>231920</t>
+          <t>231575</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>74,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>82,38%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>50723</t>
+          <t>51337</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>73943</t>
+          <t>73260</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>54839</t>
+          <t>55840</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>79158</t>
+          <t>81047</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>113958</t>
+          <t>112577</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>147795</t>
+          <t>145356</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>19,87%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>288675</t>
+          <t>289358</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>311895</t>
+          <t>311281</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>289600</t>
+          <t>287711</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>313919</t>
+          <t>312918</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>583581</t>
+          <t>586020</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>617418</t>
+          <t>618799</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,61%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>813</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4271</t>
+          <t>4334</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>73,68%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>785</t>
+          <t>773</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5163</t>
+          <t>5652</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,45%</t>
+          <t>50,86%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1526</t>
+          <t>1463</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>4984</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5950</t>
+          <t>5461</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10328</t>
+          <t>10340</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>93,04%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7693</t>
+          <t>7281</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17594</t>
+          <t>17224</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9458</t>
+          <t>8814</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20769</t>
+          <t>21465</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19213</t>
+          <t>18902</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34398</t>
+          <t>33895</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,65%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>48602</t>
+          <t>48972</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>58503</t>
+          <t>58915</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>73,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>56362</t>
+          <t>55666</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>67673</t>
+          <t>68317</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,07%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>108929</t>
+          <t>109432</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>124114</t>
+          <t>124425</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>76,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,81%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18221</t>
+          <t>17056</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36738</t>
+          <t>35893</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19334</t>
+          <t>19781</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39382</t>
+          <t>39138</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40475</t>
+          <t>39942</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>67151</t>
+          <t>65912</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>22,99%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>85165</t>
+          <t>86010</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>103682</t>
+          <t>104847</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>70,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>125406</t>
+          <t>125650</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>145454</t>
+          <t>145007</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>76,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>219540</t>
+          <t>220779</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>246216</t>
+          <t>246749</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>86,07%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21643</t>
+          <t>22169</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38248</t>
+          <t>38728</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25905</t>
+          <t>26786</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48226</t>
+          <t>49397</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>53915</t>
+          <t>53098</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>81545</t>
+          <t>81050</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,63%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>159489</t>
+          <t>159009</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>176094</t>
+          <t>175568</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>188982</t>
+          <t>187811</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>211303</t>
+          <t>210422</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>79,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>353400</t>
+          <t>353895</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>381030</t>
+          <t>381847</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,79%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>56430</t>
+          <t>54937</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>84026</t>
+          <t>82922</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>65330</t>
+          <t>63316</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>96364</t>
+          <t>94934</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>126168</t>
+          <t>129528</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>169935</t>
+          <t>169743</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,38%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>307607</t>
+          <t>308711</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>335203</t>
+          <t>336696</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>388080</t>
+          <t>389510</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>419114</t>
+          <t>421128</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>706141</t>
+          <t>706333</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>749908</t>
+          <t>746548</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,21%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP19C03-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP19C03-Edad-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -836,47 +836,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1893</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>3906</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>1893</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1893</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1893</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1893</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>3906</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>3906</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>3906</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1893</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1893</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>1893</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>7270</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3870</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>11976</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>9,04%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4,81%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>14,89%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>9703</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>6007</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>15636</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>5438</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>14965</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>11,51%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>7,12%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>18,54%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>7270</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>4030</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>11950</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>9,04%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11125</t>
+          <t>11739</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23158</t>
+          <t>24022</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,58%</t>
         </is>
       </c>
     </row>
@@ -1184,67 +1184,67 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>73148</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>68442</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>76548</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>90,96%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>85,11%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>95,19%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>74632</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>68699</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>78328</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>69370</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>78897</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>88,49%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>81,46%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>92,88%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>73148</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>68468</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>76388</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>90,96%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>82,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>141595</t>
+          <t>140731</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>153628</t>
+          <t>153014</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>92,87%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>80418</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>80418</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>80418</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>84335</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>84335</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>84335</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>80418</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>80418</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>80418</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>17652</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>12128</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>24445</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>16,7%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>11,47%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>23,12%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>19547</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>13945</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>25992</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>13993</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>26809</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>19,71%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>14,06%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>26,2%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>17652</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>12048</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>24281</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>16,7%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28967</t>
+          <t>29260</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46774</t>
+          <t>46776</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>88067</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>81274</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>93591</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>83,3%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>76,88%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>88,53%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>118</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>79646</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>73201</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>85248</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>72384</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>85200</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>80,29%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>73,8%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>85,94%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>88067</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>81438</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>93671</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>83,3%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>77,03%</t>
+          <t>72,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>158138</t>
+          <t>158136</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>175945</t>
+          <t>175652</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>85,72%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>105719</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>105719</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>105719</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>148</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>99193</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>99193</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>99193</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>105719</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>105719</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>105719</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>38549</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>30329</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>47545</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>22,19%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>17,46%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>27,37%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>43539</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>35023</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>54293</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>34942</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>53299</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>26,63%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>21,42%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>33,21%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>38549</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>29954</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>48416</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>22,19%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>69361</t>
+          <t>69839</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>95925</t>
+          <t>95299</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,26%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>135152</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>126156</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>143372</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>77,81%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>72,63%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>82,54%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>176</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>119958</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>109204</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>128474</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>110198</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>128555</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>73,37%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>66,79%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>78,58%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>135152</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>125285</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>143747</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>77,81%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>241272</t>
+          <t>241898</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>267836</t>
+          <t>267358</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>71,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>79,29%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>173701</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>173701</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>173701</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>163497</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>163497</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>163497</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>173701</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>173701</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>173701</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>63471</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>52631</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>74619</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>17,55%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>14,55%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>20,63%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>72789</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>62455</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>85858</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>60600</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>85800</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>20,74%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>17,8%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>24,47%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>63471</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>52878</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>75264</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>17,55%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>119633</t>
+          <t>119807</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>152819</t>
+          <t>155465</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,81%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>298260</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>287112</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>309100</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>82,45%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>79,37%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>85,45%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>412</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>278141</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>265072</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>288475</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>265130</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>290330</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>79,26%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>75,53%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>82,2%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>450</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>298260</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>286467</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>308853</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>82,45%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>559842</t>
+          <t>557196</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>593028</t>
+          <t>592854</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>83,19%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>522</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>350930</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>350930</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>350930</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>545</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2783,47 +2783,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>3298</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>669</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>3298</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>3298</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>3298</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>669</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>669</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>669</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>12694</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>7882</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>20085</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>13,79%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>8,56%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>21,82%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>7162</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>3660</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>12155</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>3988</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>12202</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>9,22%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4,71%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>15,65%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>12694</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>7865</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>19519</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>13,79%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13317</t>
+          <t>13993</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27304</t>
+          <t>27976</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,48%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>79370</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>71979</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>84182</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>86,21%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>78,18%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>91,44%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>70526</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>65533</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>74028</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>65486</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>73700</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>90,78%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>84,35%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95,29%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>79370</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>72545</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>84199</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>86,21%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>84,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>142447</t>
+          <t>141775</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>156434</t>
+          <t>155758</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>91,76%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>92064</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>92064</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>92064</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>77688</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>77688</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>77688</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>92064</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>92064</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>92064</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3361,67 +3361,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>25560</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>18762</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>33534</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>19,35%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>14,2%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>25,39%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>26257</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>18815</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>34443</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>18774</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>33641</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>21,1%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>15,12%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>27,68%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>25560</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>19054</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>33850</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>19,35%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>41850</t>
+          <t>41743</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>61895</t>
+          <t>62226</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,26%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>106526</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>98552</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>113324</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>80,65%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>74,61%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>85,8%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>139</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>98191</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>90005</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>105633</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>90807</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>105674</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>78,9%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>72,32%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>84,88%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>106526</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>98236</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>113032</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>80,65%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>72,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>194639</t>
+          <t>194308</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>214684</t>
+          <t>214791</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>83,73%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>132086</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>132086</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>132086</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>177</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>124448</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>124448</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>124448</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>132086</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>132086</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>132086</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>32866</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>24941</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>41382</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>23,19%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>17,59%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>29,19%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>39525</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>31584</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>48769</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>31989</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>49459</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>26,72%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>21,35%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>32,97%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>32866</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>25034</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>41954</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>23,19%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>60858</t>
+          <t>60885</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>84419</t>
+          <t>85652</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,57%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>108889</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>100373</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>116814</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>76,81%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>70,81%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>82,41%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>108395</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>99151</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>116336</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>98461</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>115931</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>73,28%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>67,03%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>78,65%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>108889</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>99801</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>116721</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>76,81%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>66,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>78,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>205256</t>
+          <t>204023</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>228817</t>
+          <t>228790</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,86%</t>
+          <t>70,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>78,98%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>141755</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>141755</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>141755</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>147920</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>147920</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>147920</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>141755</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>141755</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>141755</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>71120</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>58627</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>83973</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>19,4%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>15,99%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>22,91%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>107</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>72944</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>60546</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>84849</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>62117</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>85259</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>20,64%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>17,13%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>24,01%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>71120</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>59864</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>83812</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>19,4%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>125795</t>
+          <t>127695</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>161024</t>
+          <t>160607</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,31%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>419</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>295454</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>282601</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>307947</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>80,6%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>77,09%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>84,01%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>396</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>280409</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>268504</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>292807</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>268094</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>291236</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>79,36%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>75,99%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>82,87%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>419</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>295454</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>282762</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>306710</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>80,6%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>75,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>558903</t>
+          <t>559320</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>594132</t>
+          <t>592232</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>82,26%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>525</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>366574</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>366574</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>366574</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>503</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>353353</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>353353</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>353353</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>525</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>366574</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>366574</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>366574</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4730,47 +4730,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1284</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>536</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>1284</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1284</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1284</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1284</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>536</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>536</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>536</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1284</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1284</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>1284</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4965,67 +4965,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>11366</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6784</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>17085</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>13,84%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>8,26%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>20,8%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>10485</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>6522</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>16510</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>6334</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>16081</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>15,4%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>9,58%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>24,26%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>11366</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>6878</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>17031</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>13,84%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15313</t>
+          <t>15486</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29540</t>
+          <t>29898</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,91%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>70763</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>65044</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>75345</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>86,16%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>79,2%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>91,74%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>57575</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>51550</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>61538</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>51979</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>61726</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>84,6%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>75,74%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>90,42%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>70763</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>65098</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>75251</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>86,16%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>76,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>120649</t>
+          <t>120291</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>134876</t>
+          <t>134703</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>80,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,69%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>82129</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>82129</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>82129</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>68060</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>68060</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>68060</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>82129</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>82129</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>82129</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>24391</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>18015</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>32541</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>16,33%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>12,06%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>21,79%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>22358</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>15406</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>29752</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>15914</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>30294</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>15,01%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>10,35%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>19,98%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>24391</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>17553</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>32589</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>16,33%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37158</t>
+          <t>36844</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>59121</t>
+          <t>58195</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,51%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>124950</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>116800</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>131326</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>83,67%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>78,21%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>87,94%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>181</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>126559</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>119165</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>133511</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>118623</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>133003</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>84,99%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>80,02%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>89,65%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>124950</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>116752</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>131788</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>83,67%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>239137</t>
+          <t>240063</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>261100</t>
+          <t>261414</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>87,65%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>149341</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>149341</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>149341</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>214</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>148917</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>148917</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>148917</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>149341</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>149341</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>149341</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>31333</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>23530</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>39366</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>23,04%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>17,3%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>28,94%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>28788</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>21586</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>36508</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>20904</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>37181</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>19,84%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>14,88%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>25,16%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>31333</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>23509</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>40255</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>23,04%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>49535</t>
+          <t>50265</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>71716</t>
+          <t>72750</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,88%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>104672</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>96639</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>112475</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>76,96%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>71,06%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>82,7%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>163</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>116317</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>108597</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>123519</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>107924</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>124201</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>80,16%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>74,84%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>85,12%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>104672</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>95750</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>112496</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>76,96%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,4%</t>
+          <t>74,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>209394</t>
+          <t>208360</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>231575</t>
+          <t>230845</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>74,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>82,12%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>136005</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>136005</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>136005</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>208</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>145105</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>145105</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>145105</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>136005</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>136005</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>136005</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5994,67 +5994,67 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>67090</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>56471</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>80516</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>18,19%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>15,31%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>21,83%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>61631</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>51337</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>73260</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>49923</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>73348</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>17,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>14,16%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>20,2%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>67090</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>55840</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>81047</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>18,19%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>112577</t>
+          <t>112503</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>145356</t>
+          <t>146019</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,96%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>417</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>301668</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>288242</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>312287</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>81,81%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>78,17%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>84,69%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>433</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>300987</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>289358</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>311281</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>289270</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>312695</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>83,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>79,8%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>85,84%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>417</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>301668</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>287711</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>312918</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>81,81%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,02%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>586020</t>
+          <t>585357</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>618799</t>
+          <t>618873</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>80,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>84,62%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>368758</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>368758</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>368758</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>527</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>362618</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>362618</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>362618</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>368758</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>368758</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>368758</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2422</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>813</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4334</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>41,77%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>14,03%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>74,76%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2262</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>731</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4343</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>71,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2422</t>
+          <t>2262</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>773</t>
+          <t>697</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5652</t>
+          <t>5267</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>49,0%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3375</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1463</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4984</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>58,23%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5316</t>
+          <t>3810</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1729</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5341</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>62,75%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>8691</t>
+          <t>8486</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5461</t>
+          <t>5481</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10340</t>
+          <t>10051</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,14%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,52%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4676</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4676</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>4676</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>5797</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>5797</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5797</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5316</t>
+          <t>6072</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5316</t>
+          <t>6072</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5316</t>
+          <t>6072</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>11113</t>
+          <t>10748</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>11113</t>
+          <t>10748</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11113</t>
+          <t>10748</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>13212</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>8580</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>19723</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>19,55%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>12,7%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>29,19%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>12009</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>7281</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>17224</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>18,14%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>11,0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>26,02%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14172</t>
+          <t>12112</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8814</t>
+          <t>7641</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21465</t>
+          <t>17698</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>26181</t>
+          <t>25324</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18902</t>
+          <t>18508</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33895</t>
+          <t>33901</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>25,87%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>54358</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>47847</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>58990</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>80,45%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>70,81%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>87,3%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>54187</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>48972</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>58915</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>81,86%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>73,98%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>89,0%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>62959</t>
+          <t>51337</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>55666</t>
+          <t>45751</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>68317</t>
+          <t>55808</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>72,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>117146</t>
+          <t>105696</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>109432</t>
+          <t>97119</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>124425</t>
+          <t>112512</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>80,67%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>74,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>85,87%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>67570</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>67570</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>67570</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>103</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>66196</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>66196</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>66196</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>77131</t>
+          <t>63449</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>77131</t>
+          <t>63449</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>77131</t>
+          <t>63449</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>143327</t>
+          <t>131020</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>143327</t>
+          <t>131020</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>143327</t>
+          <t>131020</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>24914</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>16986</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>34325</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>16,04%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>10,94%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>22,1%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>24713</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>17056</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>35893</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>20,27%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>13,99%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>29,44%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>28221</t>
+          <t>22476</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19781</t>
+          <t>15811</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39138</t>
+          <t>30331</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>52934</t>
+          <t>47390</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>39942</t>
+          <t>38410</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>65912</t>
+          <t>60307</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>21,76%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>130384</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>120973</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>138312</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>83,96%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>77,9%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>89,06%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>132</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>97190</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>86010</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>104847</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>79,73%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>70,56%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>86,01%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>136567</t>
+          <t>99364</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>125650</t>
+          <t>91509</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>145007</t>
+          <t>106029</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>75,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>233757</t>
+          <t>229748</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>220779</t>
+          <t>216831</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>246749</t>
+          <t>238728</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>78,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>86,14%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>155298</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>155298</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>155298</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>163</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>121903</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>121903</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>121903</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>164788</t>
+          <t>121840</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>164788</t>
+          <t>121840</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>164788</t>
+          <t>121840</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>286691</t>
+          <t>277138</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>286691</t>
+          <t>277138</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>286691</t>
+          <t>277138</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>29762</t>
+          <t>34745</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22169</t>
+          <t>25348</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38728</t>
+          <t>46847</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>36395</t>
+          <t>30461</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26786</t>
+          <t>22417</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49397</t>
+          <t>39460</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>66158</t>
+          <t>65206</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>53098</t>
+          <t>52163</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>81050</t>
+          <t>80036</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,25%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>198805</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>186703</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>208202</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>85,12%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>79,94%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>89,15%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>167975</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>159009</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>175568</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>84,95%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>80,41%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>88,79%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>200813</t>
+          <t>174455</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>187811</t>
+          <t>165456</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>210422</t>
+          <t>182499</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>368787</t>
+          <t>373260</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>353895</t>
+          <t>358430</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>381847</t>
+          <t>386303</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>81,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>88,1%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>233550</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>233550</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>233550</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>277</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>197737</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>197737</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>197737</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>237208</t>
+          <t>204916</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>237208</t>
+          <t>204916</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>237208</t>
+          <t>204916</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>434945</t>
+          <t>438466</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>434945</t>
+          <t>438466</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>434945</t>
+          <t>438466</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>72870</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>58072</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>88226</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>15,8%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>12,59%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>19,13%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>68906</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>54937</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>82922</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>17,59%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>14,03%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>21,17%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>78788</t>
+          <t>67312</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>63316</t>
+          <t>55645</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>94934</t>
+          <t>79711</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>147694</t>
+          <t>140182</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>129528</t>
+          <t>122944</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>169743</t>
+          <t>160070</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>18,67%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>475</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>388225</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>372869</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>403023</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>84,2%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>80,87%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>87,41%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>457</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>322727</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>308711</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>336696</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>82,41%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>78,83%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>85,97%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>475</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>405656</t>
+          <t>328966</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>389510</t>
+          <t>316567</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>421128</t>
+          <t>340633</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>728382</t>
+          <t>717190</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>706333</t>
+          <t>697302</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>746548</t>
+          <t>734428</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>81,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>85,66%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>554</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>570</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
